--- a/高经济价值第六期_销售佣金清算/销售佣金清算_v1_标准答案.xlsx
+++ b/高经济价值第六期_销售佣金清算/销售佣金清算_v1_标准答案.xlsx
@@ -223,7 +223,163 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm11.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="100000" y="100000"/>
@@ -379,7 +535,163 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="100000" y="100000"/>
@@ -535,7 +847,163 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="100000" y="100000"/>
@@ -691,6 +1159,110 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
@@ -744,6 +1316,110 @@
 </file>
 
 <file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="100000" y="100000"/>

--- a/高经济价值第六期_销售佣金清算/销售佣金清算_v1_标准答案.xlsx
+++ b/高经济价值第六期_销售佣金清算/销售佣金清算_v1_标准答案.xlsx
@@ -275,6 +275,58 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
@@ -328,6 +380,110 @@
 </file>
 
 <file path=xl/drawings/drawing_wm10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm11.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="100000" y="100000"/>
@@ -587,6 +743,58 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
@@ -640,6 +848,110 @@
 </file>
 
 <file path=xl/drawings/drawing_wm13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="100000" y="100000"/>
@@ -899,6 +1211,58 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
@@ -952,6 +1316,110 @@
 </file>
 
 <file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="100000" y="100000"/>
@@ -1211,6 +1679,110 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
@@ -1368,6 +1940,110 @@
 </file>
 
 <file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="100000" y="100000"/>
